--- a/test-workflow-docker/ig/StructureDefinition-as-ext-organization-pharmacy-licence.xlsx
+++ b/test-workflow-docker/ig/StructureDefinition-as-ext-organization-pharmacy-licence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T10:32:14+00:00</t>
+    <t>2026-06-25T12:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
